--- a/treinos/fonte/Treinos.xlsx
+++ b/treinos/fonte/Treinos.xlsx
@@ -345,7 +345,7 @@
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,5 km aquecimento
-1,5 km Tempo curto (ST)
+1,5 km em ST
 1,5 km desaquecimento</t>
         </is>
       </c>
@@ -403,7 +403,7 @@
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,5 km aquecimento
-1,5 km Tempo curto (ST)
+1,5 km em ST
 1,5 km desaquecimento</t>
         </is>
       </c>
@@ -461,7 +461,7 @@
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,5 km aquecimento
-1,5 km Tempo curto (ST)
+1,5 km em ST
 1,5 km desaquecimento</t>
         </is>
       </c>
@@ -519,7 +519,7 @@
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,5 km aquecimento
-2 km Tempo curto (ST)
+2 km em ST
 1,5 km desaquecimento</t>
         </is>
       </c>
@@ -573,7 +573,7 @@
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,5 km aquecimento
-2 km Tempo curto (ST)
+2 km em ST
 1,5 km desaquecimento</t>
         </is>
       </c>
@@ -630,7 +630,7 @@
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,5 km aquecimento
-1,5 km Tempo curto (ST)
+1,5 km em ST
 1,5 km desaquecimento</t>
         </is>
       </c>
@@ -684,7 +684,7 @@
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,5 km aquecimento
-2 km Tempo curto (ST)
+2 km em ST
 1,5 km desaquecimento</t>
         </is>
       </c>
@@ -740,7 +740,7 @@
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,5 km aquecimento
-3 km Tempo curto (ST)
+3 km em ST
 1,5 km desaquecimento</t>
         </is>
       </c>
@@ -794,7 +794,7 @@
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,5 km aquecimento
-3 km Tempo curto (ST)
+3 km em ST
 1,5 km desaquecimento</t>
         </is>
       </c>
@@ -850,7 +850,7 @@
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1,5 km aquecimento
-3 km Tempo curto (ST)
+3 km em ST
 1,5 km desaquecimento</t>
         </is>
       </c>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 x (6 x 400) (90 s RI) (2 min 30 s RI between sets)</t>
+          <t xml:space="preserve">2 x (6 x 400) (90 s RI) (2 min 30 s RI entre as séries)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aquecimento 10 min, 5K em MP, Desaquecimento 10 min</t>
+          <t xml:space="preserve">Aquecimento 10 min, 5 km em MP, Desaquecimento 10 min</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notação das semanas 1 a 3. Interpretação: W = caminhada, R = corrida (ex.: "W:10min R:3K W:5min"). Confirme com a fonte original do plano.</t>
+          <t xml:space="preserve">Notação das semanas 1 a 3. Interpretação: W = caminhada, R = corrida (ex.: "W:10min R:3K W:5min").</t>
         </is>
       </c>
     </row>
